--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-dicom-medication-administration.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-dicom-medication-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:33:22+00:00</t>
+    <t>2026-04-24T13:15:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-dicom-medication-administration.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-dicom-medication-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:15:59+00:00</t>
+    <t>2026-04-29T08:17:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,11 +269,11 @@
     <t>fr-lm-dicom-medication-administration.header.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient-usager
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient
 </t>
   </si>
   <si>
-    <t>Patient/subject information</t>
+    <t>Patient / Usager</t>
   </si>
   <si>
     <t>fr-lm-entry.header.subject</t>
@@ -443,7 +443,7 @@
     <t>fr-lm-entry.header.source</t>
   </si>
   <si>
-    <t>fr-lm-dicom-medication-administration.header.langue</t>
+    <t>fr-lm-dicom-medication-administration.header.language</t>
   </si>
   <si>
     <t>'fr-FR' pour français métropolitain (la casse des caractères doit être respectée)
@@ -451,7 +451,7 @@
 La partie en majuscules indique le code pays (ISO-3166)</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.langue</t>
+    <t>fr-lm-entry.header.language</t>
   </si>
   <si>
     <t>fr-lm-dicom-medication-administration.voieAdministration</t>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-dicom-medication-administration.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-dicom-medication-administration.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="194">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:17:29+00:00</t>
+    <t>2026-04-29T08:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -422,13 +422,7 @@
 </t>
   </si>
   <si>
-    <t>Statut de l'acte</t>
-  </si>
-  <si>
-    <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis</t>
+    <t>Statut</t>
   </si>
   <si>
     <t>fr-lm-entry.header.status</t>
@@ -952,7 +946,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="68.90234375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.58203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -2587,7 +2581,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>79</v>
@@ -2638,31 +2632,31 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="Z17" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>135</v>
-      </c>
       <c r="AG17" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>79</v>
@@ -2676,10 +2670,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2705,10 +2699,10 @@
         <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2759,7 +2753,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2776,10 +2770,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2805,10 +2799,10 @@
         <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2859,7 +2853,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2876,10 +2870,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2905,10 +2899,10 @@
         <v>131</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2938,7 +2932,7 @@
         <v>73</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Z20" t="s" s="2">
         <v>73</v>
@@ -2959,7 +2953,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
@@ -2976,10 +2970,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3002,13 +2996,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3059,7 +3053,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -3076,10 +3070,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3102,13 +3096,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3159,7 +3153,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3176,10 +3170,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3205,10 +3199,10 @@
         <v>80</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3259,7 +3253,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -3276,10 +3270,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3305,10 +3299,10 @@
         <v>80</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3359,7 +3353,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -3376,10 +3370,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3405,10 +3399,10 @@
         <v>131</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3438,7 +3432,7 @@
         <v>73</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="Z25" t="s" s="2">
         <v>73</v>
@@ -3459,7 +3453,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3471,15 +3465,15 @@
         <v>73</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3502,13 +3496,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3559,7 +3553,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3576,14 +3570,14 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -3602,16 +3596,16 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>169</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -3649,19 +3643,19 @@
         <v>73</v>
       </c>
       <c r="AB27" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE27" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="AC27" t="s" s="2">
+      <c r="AF27" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3673,15 +3667,15 @@
         <v>73</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3701,22 +3695,22 @@
         <v>73</v>
       </c>
       <c r="J28" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="K28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>73</v>
@@ -3765,7 +3759,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -3777,15 +3771,15 @@
         <v>73</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3805,22 +3799,22 @@
         <v>73</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>73</v>
@@ -3869,7 +3863,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -3881,15 +3875,15 @@
         <v>73</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3915,10 +3909,10 @@
         <v>131</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3948,7 +3942,7 @@
         <v>73</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="Z30" t="s" s="2">
         <v>73</v>
@@ -3969,7 +3963,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -3986,10 +3980,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4012,13 +4006,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4069,7 +4063,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4086,10 +4080,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4112,13 +4106,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4169,7 +4163,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-dicom-medication-administration.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-dicom-medication-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:41:15+00:00</t>
+    <t>2026-04-30T08:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
